--- a/Labs/7.AWS_Architecture_Lab/AWS_Team_Allocations_And_Review.xlsx
+++ b/Labs/7.AWS_Architecture_Lab/AWS_Team_Allocations_And_Review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Online Training\Apexon\GS-Training\Labs\7.AWS_Architecture_Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219AADEE-1D9B-4F5F-9CB9-E8968B79A362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D587646-52F2-419F-AC40-E9400BEBDD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AWS_DEV_Team1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="54">
   <si>
     <t>Serial No.</t>
   </si>
@@ -190,6 +190,19 @@
   </si>
   <si>
     <t>Justify use of NACL</t>
+  </si>
+  <si>
+    <t>VPC boundary 
+Subnets 
+Public Subnet: Internet‑facing components (e.g., API Gateway edge/WAF or ALB if used).
+Private App Subnet: Step Functions, Lambda tasks (Extract/Compute), and service‑to‑service calls.
+Private Data Subnet: RDS PostgreSQL, DynamoDB interface endpoints, and Batch compute ENIs.</t>
+  </si>
+  <si>
+    <t>Be clear what "Async" represents and how it is implemented.</t>
+  </si>
+  <si>
+    <t>Redo High Level Architecture diagram as below:</t>
   </si>
 </sst>
 </file>
@@ -257,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -279,6 +292,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -926,23 +942,28 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E6B9471-97A6-401C-A3A5-A502DBC3C688}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="2" max="2" width="33.42578125" customWidth="1"/>
     <col min="3" max="3" width="21.85546875" customWidth="1"/>
+    <col min="4" max="4" width="70.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -952,24 +973,33 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -977,7 +1007,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -985,20 +1015,26 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="10" t="s">
         <v>36</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
